--- a/timesheet/excel_files/activities.xlsx
+++ b/timesheet/excel_files/activities.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNB-IT\Documents\code\timesheets_app_no_docker\timesheets_main\timesheet\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF6BD78-855C-4D9E-B5B9-506E2ED6C1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B874A923-9F3E-4268-B6D2-14E75FA41732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,15 +30,9 @@
     <t>1.1.1</t>
   </si>
   <si>
-    <t>Inventariere/identificare specii de floră</t>
-  </si>
-  <si>
     <t>1.1.2</t>
   </si>
   <si>
-    <t>Inventariere/identificare specii de faună</t>
-  </si>
-  <si>
     <t>1.1.3</t>
   </si>
   <si>
@@ -48,15 +42,9 @@
     <t>1.1.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Cartare distribuție specii de floră </t>
-  </si>
-  <si>
     <t>1.1.5</t>
   </si>
   <si>
-    <t>Cartare distribuție specii de faună</t>
-  </si>
-  <si>
     <t>1.1.6</t>
   </si>
   <si>
@@ -72,20 +60,6 @@
     <t>1.1.8</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Cartarea arealelor afectate de procese naturale/antropice </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">(avalanșe, eroziune, alunecări de teren, incendii, poluări etc.) </t>
-    </r>
-  </si>
-  <si>
     <t>1.1.9</t>
   </si>
   <si>
@@ -95,21 +69,12 @@
     <t>1.1.10</t>
   </si>
   <si>
-    <t>Cartarea distribuției speciilor invazive</t>
-  </si>
-  <si>
     <t>1.2.1</t>
   </si>
   <si>
-    <t>Monitorizare specii de floră</t>
-  </si>
-  <si>
     <t>1.2.2</t>
   </si>
   <si>
-    <t>Monitorizare specii de faună</t>
-  </si>
-  <si>
     <t>1.2.3</t>
   </si>
   <si>
@@ -137,9 +102,6 @@
     <t>1.2.7</t>
   </si>
   <si>
-    <t>Monitorizare atacuri de dăunători (Ips, Lymantria etc.)</t>
-  </si>
-  <si>
     <t>1.2.8</t>
   </si>
   <si>
@@ -149,74 +111,33 @@
     <t>1.3.1</t>
   </si>
   <si>
-    <t>Acțiuni de patrulare și/sau control pentru prevenire/combatere fapte ilegale (AP)</t>
-  </si>
-  <si>
     <t>1.3.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Încheiere protocoale de colaborare cu autorități cu competențe de control  </t>
-  </si>
-  <si>
     <t>1.3.3</t>
   </si>
   <si>
-    <t>Acțiuni de patrulare și/sau control realizate cu autorități cu competente de control (AP+alții)</t>
-  </si>
-  <si>
     <t>1.3.4</t>
   </si>
   <si>
-    <t>Reglementare activități/planuri/proiecte în cadrul procedurilor de reglementare</t>
-  </si>
-  <si>
     <t>1.3.5</t>
   </si>
   <si>
-    <t>Reglementare activități/planuri/proiecte în afara procedurilor de reglementare</t>
-  </si>
-  <si>
     <t>1.3.6</t>
   </si>
   <si>
-    <t>Emitere condiții specifice la punerea în valoare/ exploatarea masei lemnoase</t>
-  </si>
-  <si>
     <t>1.3.7</t>
   </si>
   <si>
-    <t>Verificarea respectării condițiilor prevăzute prin avize/acorduri, condiții specifice</t>
-  </si>
-  <si>
     <t>1.3.8</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Verificare respectare măsuri de management specifice </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(ex. începerea pășunatului după….)</t>
-    </r>
-  </si>
-  <si>
     <t>1.3.9</t>
   </si>
   <si>
-    <t>Participare la acțiuni de evaluare a speciilor de interes cinegetic</t>
-  </si>
-  <si>
     <t>1.3.10</t>
   </si>
   <si>
-    <t xml:space="preserve">Materializare/refacere în teren a limitelor AP/zonarii parcului </t>
-  </si>
-  <si>
     <t>1.3.11</t>
   </si>
   <si>
@@ -226,20 +147,6 @@
     <t>1.3.12</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Realizare infrastructură de prevenție </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(bariere, porți, grilaje etc.)</t>
-    </r>
-  </si>
-  <si>
     <t>1.4.1</t>
   </si>
   <si>
@@ -249,178 +156,45 @@
     <t>1.4.2</t>
   </si>
   <si>
-    <t>Actualizare bază de date privind inventarierea și/sau cartografierea speciilor de floră</t>
-  </si>
-  <si>
     <t>1.4.3</t>
   </si>
   <si>
-    <t>Actualizare bază de date privind inventarierea și/sau cartografierea speciilor de faună</t>
-  </si>
-  <si>
     <t>1.4.4</t>
   </si>
   <si>
-    <t>Actualizare bază de date privind inventarierea și/sau cartografierea habitatelor naturale</t>
-  </si>
-  <si>
     <t>1.4.5</t>
   </si>
   <si>
-    <t>Actualizare bază de date privind monitorizarea speciilor de floră</t>
-  </si>
-  <si>
     <t>1.4.6</t>
   </si>
   <si>
-    <t>Actualizare bază de date privind monitorizarea speciilor de faună</t>
-  </si>
-  <si>
     <t>1.4.7</t>
   </si>
   <si>
-    <t>Actualizare bază de date privind monitorizarea habitatelor naturale</t>
-  </si>
-  <si>
     <t>1.5.1</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Elaborare studiu pentru reintroducerea speciei dispărute </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(ex.: zimbru)</t>
-    </r>
-  </si>
-  <si>
     <t>1.5.2</t>
   </si>
   <si>
-    <t>Implementare activități specifice</t>
-  </si>
-  <si>
     <t>1.6.1</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Identificarea habitatelor naturale ce necesită reconstrucție ecologică </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(ex.: restaurare zone umede, combatere specii invazive)</t>
-    </r>
-  </si>
-  <si>
     <t>1.6.2</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Identificarea terenurilor degradate </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">(halde de steril, suprafețe afectate de eroziune </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>etc.</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
     <t>1.6.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Reconstrucția ecologică </t>
-  </si>
-  <si>
     <t>1.6.4</t>
   </si>
   <si>
-    <t>Monitorizarea suprafețe reconstruite ecologic</t>
-  </si>
-  <si>
     <t>2.1.1</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Realizarea/amenajarea infrastructurii de vizitare/informare </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">(centru de vizitare, punct de informare, refugii, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="238"/>
-      </rPr>
-      <t>infochioșcuri)</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-  </si>
-  <si>
     <t>2.1.2</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Reparare și întreținere infrastructură de vizitare </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">(centru de vizitare, punct de informare, refugii, infochioscuri)                                                       </t>
-    </r>
-  </si>
-  <si>
     <t>2.1.3</t>
   </si>
   <si>
@@ -430,9 +204,6 @@
     <t>2.1.4</t>
   </si>
   <si>
-    <t>Întreținere/reparare panouri informative</t>
-  </si>
-  <si>
     <t>2.1.5</t>
   </si>
   <si>
@@ -442,9 +213,6 @@
     <t>2.1.6</t>
   </si>
   <si>
-    <t>Întreținere trasee turistice</t>
-  </si>
-  <si>
     <t>2.1.7</t>
   </si>
   <si>
@@ -454,9 +222,6 @@
     <t>2.1.8</t>
   </si>
   <si>
-    <t>Întreținere trasee/poteci tematice</t>
-  </si>
-  <si>
     <t>2.1.9</t>
   </si>
   <si>
@@ -466,9 +231,6 @@
     <t>2.1.10</t>
   </si>
   <si>
-    <t>Întreținere trasee cicloturism/ecvestre</t>
-  </si>
-  <si>
     <t>2.1.11</t>
   </si>
   <si>
@@ -478,21 +240,12 @@
     <t>2.1.12</t>
   </si>
   <si>
-    <t>Întreținere locuri de campare</t>
-  </si>
-  <si>
     <t>2.1.13</t>
   </si>
   <si>
-    <t>Amenajare puncte de belvedere și popas</t>
-  </si>
-  <si>
     <t>2.1.14</t>
   </si>
   <si>
-    <t>Întreținere puncte de belvedere și popas</t>
-  </si>
-  <si>
     <t>2.1.15</t>
   </si>
   <si>
@@ -500,20 +253,6 @@
   </si>
   <si>
     <t>2.2.1</t>
-  </si>
-  <si>
-    <r>
-      <t>Elaborare materiale promovare</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (album, ghid, hărți, poster, pliant, atlas, film, broșuri etc.)</t>
-    </r>
   </si>
   <si>
     <t>2.2.2</t>
@@ -536,9 +275,6 @@
     <t>2.2.3</t>
   </si>
   <si>
-    <t>Asigurare servicii de ghidare/însoțire a vizitatorilor</t>
-  </si>
-  <si>
     <t>2.3.1</t>
   </si>
   <si>
@@ -548,9 +284,6 @@
     <t>2.3.2</t>
   </si>
   <si>
-    <t>Monitorizare vizitatori prin observații directe pe teren</t>
-  </si>
-  <si>
     <t>2.3.3</t>
   </si>
   <si>
@@ -572,9 +305,6 @@
     <t>3.1.2</t>
   </si>
   <si>
-    <t>Participare la evenimente culturale și tradiționale</t>
-  </si>
-  <si>
     <t>3.1.3</t>
   </si>
   <si>
@@ -584,44 +314,18 @@
     <t>3.2.1</t>
   </si>
   <si>
-    <t>Organizare acțiuni de conștientizare</t>
-  </si>
-  <si>
     <t>3.2.2</t>
   </si>
   <si>
-    <t>Editare și publicare buletin informativ</t>
-  </si>
-  <si>
     <t>3.2.3</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Organizare evenimente </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(Ziua Europeană a Parcurilor/ Parcului, Ziua zonelor umede etc.)</t>
-    </r>
-  </si>
-  <si>
     <t>3.2.4</t>
   </si>
   <si>
-    <t>Participare la simpozioane, întâlniri tematice, conferinţe, manifestări în ţară şi străinătate</t>
-  </si>
-  <si>
     <t>3.2.5</t>
   </si>
   <si>
-    <t>Publicare articole în mass-media</t>
-  </si>
-  <si>
     <t>3.2.6</t>
   </si>
   <si>
@@ -631,9 +335,6 @@
     <t>3.2.7</t>
   </si>
   <si>
-    <t>Actualizare pagină web/Facebook</t>
-  </si>
-  <si>
     <t>3.3.1</t>
   </si>
   <si>
@@ -643,38 +344,15 @@
     <t>3.3.2</t>
   </si>
   <si>
-    <t>Realizare acțiuni de educație ecologică</t>
-  </si>
-  <si>
     <t>3.3.3</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Realizare materiale pentru educație ecologică </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(album, ghid, hărți, poster, atlas, film, broșură, pliant, afiș, flyer, revistă etc.)</t>
-    </r>
-  </si>
-  <si>
     <t>3.3.4</t>
   </si>
   <si>
-    <t>Realizare manual de educație ecologică</t>
-  </si>
-  <si>
     <t>4.1.1</t>
   </si>
   <si>
-    <t>Dotare cu echipament vestimentar și de protecție</t>
-  </si>
-  <si>
     <t>4.1.2</t>
   </si>
   <si>
@@ -682,9 +360,6 @@
   </si>
   <si>
     <t>4.1.3</t>
-  </si>
-  <si>
-    <t>Dotări IT, inclusiv soft-uri</t>
   </si>
   <si>
     <t>4.1.4</t>
@@ -713,21 +388,12 @@
     <t>4.2.1</t>
   </si>
   <si>
-    <t>Organizare întâlniri Consiliul Științific</t>
-  </si>
-  <si>
     <t>4.2.2</t>
   </si>
   <si>
-    <t>Organizare întâlniri Consiliul Consultativ de Administrare</t>
-  </si>
-  <si>
     <t>4.2.3</t>
   </si>
   <si>
-    <t>Organizare ședințe Comitet Director (CD)</t>
-  </si>
-  <si>
     <t>4.2.4</t>
   </si>
   <si>
@@ -737,57 +403,15 @@
     <t>4.2.5</t>
   </si>
   <si>
-    <t>Întocmire Raport anual de activitate</t>
-  </si>
-  <si>
     <t>4.2.6</t>
   </si>
   <si>
-    <r>
-      <t>Accesare fonduri externe</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Life, INTERREG, PDD, SEE/EEA etc.) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>individual sau în parteneriat</t>
-    </r>
-  </si>
-  <si>
     <t>4.2.8</t>
   </si>
   <si>
-    <t>Implicare voluntari în managementul AP</t>
-  </si>
-  <si>
     <t>4.2.9</t>
   </si>
   <si>
-    <r>
-      <t>Încheierea de parteneriate/acorduri cu terți în vederea implementării de activități</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (cercetare, turism, educație ecologică etc.)</t>
-    </r>
-  </si>
-  <si>
     <t>4.3.1</t>
   </si>
   <si>
@@ -827,60 +451,25 @@
     <t>4.3.7</t>
   </si>
   <si>
-    <t>Elaborare Strategie de comunicare, conștientizare și educație ecologică</t>
-  </si>
-  <si>
     <t>4.3.8</t>
   </si>
   <si>
-    <t>Elaborare Plan de educație ecologică</t>
-  </si>
-  <si>
     <t>4.3.9</t>
   </si>
   <si>
-    <t>Elaborare Plan de comunicare și conștientizare</t>
-  </si>
-  <si>
     <t>4.3.10</t>
   </si>
   <si>
-    <t>Elaborare Plan anual de investiții</t>
-  </si>
-  <si>
     <t>4.3.11</t>
   </si>
   <si>
-    <t>Elaborare Plan anual de achiziții</t>
-  </si>
-  <si>
     <t>4.3.12</t>
   </si>
   <si>
-    <t>Elaborare și implementare Program privind Controlul intern managerial</t>
-  </si>
-  <si>
     <t>4.3.13</t>
   </si>
   <si>
-    <t>Elaborare Plan de pregătire profesională</t>
-  </si>
-  <si>
     <t>4.4.1.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Instruirea personalului prin participarea la cursuri, seminarii, instruiri pe domenii precum: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>achiziții, comunicare, management, GIS, turism, monitorizare etc.</t>
-    </r>
   </si>
   <si>
     <t>4.4.2.</t>
@@ -903,37 +492,239 @@
     <t>4.4.3.</t>
   </si>
   <si>
-    <t>Participarea la schimburi de experiență</t>
-  </si>
-  <si>
     <t>4.4.4.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Instruirea internă a personalului </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(legislația specifică, proceduri, protocoale de monitorizare etc.)</t>
-    </r>
-  </si>
-  <si>
     <t>code</t>
   </si>
   <si>
     <t>name</t>
+  </si>
+  <si>
+    <t>Participare la simpozioane, intalniri tematice, conferinte, manifestari in tara si strainatate</t>
+  </si>
+  <si>
+    <t>Inventariere/identificare specii de flora</t>
+  </si>
+  <si>
+    <t>Inventariere/identificare specii de fauna</t>
+  </si>
+  <si>
+    <t>Monitorizare specii de flora</t>
+  </si>
+  <si>
+    <t>Monitorizare specii de fauna</t>
+  </si>
+  <si>
+    <t>Monitorizare atacuri de daunatori (Ips, Lymantria etc.)</t>
+  </si>
+  <si>
+    <t>Actualizare baza de date privind monitorizarea speciilor de flora</t>
+  </si>
+  <si>
+    <t>Actualizare baza de date privind monitorizarea speciilor de fauna</t>
+  </si>
+  <si>
+    <t>Actualizare baza de date privind monitorizarea habitatelor naturale</t>
+  </si>
+  <si>
+    <t>Elaborare studiu pentru reintroducerea speciei disparute (ex.: zimbru)</t>
+  </si>
+  <si>
+    <t>Organizare evenimente (Ziua Europeana a Parcurilor/ Parcului, Ziua zonelor umede etc.)</t>
+  </si>
+  <si>
+    <t>Actualizare pagina web/Facebook</t>
+  </si>
+  <si>
+    <t>Dotari IT, inclusiv soft-uri</t>
+  </si>
+  <si>
+    <t>Elaborare Plan de pregatire profesionala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartare distributie specii de flora </t>
+  </si>
+  <si>
+    <t>Cartare distributie specii de fauna</t>
+  </si>
+  <si>
+    <t>Cartarea distributiei speciilor invazive</t>
+  </si>
+  <si>
+    <t>Verificarea respectarii conditiilor prevazute prin avize/acorduri, conditii specifice</t>
+  </si>
+  <si>
+    <t>Participare la actiuni de evaluare a speciilor de interes cinegetic</t>
+  </si>
+  <si>
+    <t>Realizare infrastructura de preventie (bariere, porti, grilaje etc.)</t>
+  </si>
+  <si>
+    <t>Implementare activitati specifice</t>
+  </si>
+  <si>
+    <t>Identificarea habitatelor naturale ce necesita reconstructie ecologica (ex.: restaurare zone umede, combatere specii invazive)</t>
+  </si>
+  <si>
+    <t>Identificarea terenurilor degradate (halde de steril, suprafete afectate de eroziune etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconstructia ecologica </t>
+  </si>
+  <si>
+    <t>Monitorizarea suprafete reconstruite ecologic</t>
+  </si>
+  <si>
+    <t>Monitorizare vizitatori prin observatii directe pe teren</t>
+  </si>
+  <si>
+    <t>Realizare actiuni de educatie ecologica</t>
+  </si>
+  <si>
+    <t>Realizare manual de educatie ecologica</t>
+  </si>
+  <si>
+    <t>Elaborare Plan de educatie ecologica</t>
+  </si>
+  <si>
+    <t>Elaborare Plan anual de investitii</t>
+  </si>
+  <si>
+    <t>Elaborare Plan anual de achizitii</t>
+  </si>
+  <si>
+    <t>Instruirea personalului prin participarea la cursuri, seminarii, instruiri pe domenii precum: achizitii, comunicare, management, GIS, turism, monitorizare etc.</t>
+  </si>
+  <si>
+    <t>Participarea la schimburi de experienta</t>
+  </si>
+  <si>
+    <t>Instruirea interna a personalului (legislatia specifica, proceduri, protocoale de monitorizare etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartarea arealelor afectate de procese naturale/antropice (avalanse, eroziune, alunecari de teren, incendii, poluari etc.) </t>
+  </si>
+  <si>
+    <t>Actiuni de patrulare si/sau control pentru prevenire/combatere fapte ilegale (AP)</t>
+  </si>
+  <si>
+    <t>Actiuni de patrulare si/sau control realizate cu autoritati cu competente de control (AP+altii)</t>
+  </si>
+  <si>
+    <t>Actualizare baza de date privind inventarierea si/sau cartografierea speciilor de flora</t>
+  </si>
+  <si>
+    <t>Actualizare baza de date privind inventarierea si/sau cartografierea speciilor de fauna</t>
+  </si>
+  <si>
+    <t>Actualizare baza de date privind inventarierea si/sau cartografierea habitatelor naturale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizarea/amenajarea infrastructurii de vizitare/informare (centru de vizitare, punct de informare, refugii, infochioscuri)       </t>
+  </si>
+  <si>
+    <t>Amenajare puncte de belvedere si popas</t>
+  </si>
+  <si>
+    <t>Elaborare materiale promovare (album, ghid, harti, poster, pliant, atlas, film, brosuri etc.)</t>
+  </si>
+  <si>
+    <t>Participare la evenimente culturale si traditionale</t>
+  </si>
+  <si>
+    <t>Organizare actiuni de constientizare</t>
+  </si>
+  <si>
+    <t>Editare si publicare buletin informativ</t>
+  </si>
+  <si>
+    <t>Realizare materiale pentru educatie ecologica (album, ghid, harti, poster, atlas, film, brosura, pliant, afis, flyer, revista etc.)</t>
+  </si>
+  <si>
+    <t>Dotare cu echipament vestimentar si de protectie</t>
+  </si>
+  <si>
+    <t>Organizare sedinte Comitet Director (CD)</t>
+  </si>
+  <si>
+    <t>Elaborare Strategie de comunicare, constientizare si educatie ecologica</t>
+  </si>
+  <si>
+    <t>Elaborare Plan de comunicare si constientizare</t>
+  </si>
+  <si>
+    <t>Elaborare si implementare Program privind Controlul intern managerial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incheiere protocoale de colaborare cu autoritati cu competente de control  </t>
+  </si>
+  <si>
+    <t>Reglementare activitati/planuri/proiecte in cadrul procedurilor de reglementare</t>
+  </si>
+  <si>
+    <t>Reglementare activitati/planuri/proiecte in afara procedurilor de reglementare</t>
+  </si>
+  <si>
+    <t>Emitere conditii specifice la punerea in valoare/ exploatarea masei lemnoase</t>
+  </si>
+  <si>
+    <t>Verificare respectare masuri de management specifice (ex. inceperea pasunatului dupa….)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materializare/refacere in teren a limitelor AP/zonarii parcului </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reparare si intretinere infrastructura de vizitare (centru de vizitare, punct de informare, refugii, infochioscuri)                                                       </t>
+  </si>
+  <si>
+    <t>intretinere/reparare panouri informative</t>
+  </si>
+  <si>
+    <t>intretinere trasee turistice</t>
+  </si>
+  <si>
+    <t>intretinere trasee/poteci tematice</t>
+  </si>
+  <si>
+    <t>intretinere trasee cicloturism/ecvestre</t>
+  </si>
+  <si>
+    <t>intretinere locuri de campare</t>
+  </si>
+  <si>
+    <t>intretinere puncte de belvedere si popas</t>
+  </si>
+  <si>
+    <t>Asigurare servicii de ghidare/insotire a vizitatorilor</t>
+  </si>
+  <si>
+    <t>Publicare articole in mass-media</t>
+  </si>
+  <si>
+    <t>Organizare intalniri Consiliul stiintific</t>
+  </si>
+  <si>
+    <t>Organizare intalniri Consiliul Consultativ de Administrare</t>
+  </si>
+  <si>
+    <t>intocmire Raport anual de activitate</t>
+  </si>
+  <si>
+    <t>Accesare fonduri externe (Life, INTERREG, PDD, SEE/EEA etc.) individual sau in parteneriat</t>
+  </si>
+  <si>
+    <t>Implicare voluntari in managementul AP</t>
+  </si>
+  <si>
+    <t>incheierea de parteneriate/acorduri cu terti in vederea implementarii de activitati (cercetare, turism, educatie ecologica etc.)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -970,13 +761,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <i/>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1024,24 +808,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1331,886 +1116,887 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" t="s">
-        <v>219</v>
+      <c r="A1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="77.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="62" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="62" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="9" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="62" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="62" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
+      <c r="B11" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="186" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B29" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+      <c r="B30" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="3" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="217" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="155" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="155" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="186" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="186" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="232.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="155" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="124" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="186" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="155" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>59</v>
+      <c r="B31" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="62" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="50" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+      <c r="B50" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="186" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="124" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="124" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="62" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="217" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="62" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="263.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="248" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="93" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>101</v>
+        <v>64</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>103</v>
+        <v>65</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>105</v>
+        <v>67</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>107</v>
+        <v>68</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>109</v>
+        <v>70</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>111</v>
+        <v>71</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>113</v>
+        <v>72</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>115</v>
+        <v>73</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>117</v>
+        <v>75</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>119</v>
+        <v>76</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>121</v>
+        <v>78</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>123</v>
+        <v>79</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>125</v>
+        <v>81</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>127</v>
+        <v>82</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>129</v>
+        <v>84</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>131</v>
+        <v>86</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>133</v>
+        <v>88</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>135</v>
+        <v>89</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>137</v>
+        <v>91</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>139</v>
+        <v>92</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>141</v>
+        <v>93</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>143</v>
+        <v>94</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>145</v>
+        <v>95</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>147</v>
+        <v>96</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>151</v>
+        <v>99</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>153</v>
+        <v>101</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>155</v>
+        <v>102</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>157</v>
+        <v>103</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>159</v>
+        <v>104</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>161</v>
+        <v>105</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>163</v>
+        <v>107</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>165</v>
+        <v>108</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>167</v>
+        <v>110</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>169</v>
+        <v>112</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>171</v>
+        <v>113</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>173</v>
+        <v>114</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>175</v>
+        <v>115</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>177</v>
+        <v>117</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>179</v>
+        <v>118</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>181</v>
+        <v>119</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>183</v>
+        <v>120</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>185</v>
+        <v>121</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>187</v>
+        <v>123</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>189</v>
+        <v>125</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>191</v>
+        <v>127</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>193</v>
+        <v>129</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>195</v>
+        <v>131</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>199</v>
+        <v>134</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>201</v>
+        <v>135</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>203</v>
+        <v>136</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>205</v>
+        <v>137</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>207</v>
+        <v>138</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>209</v>
+        <v>139</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>211</v>
+        <v>140</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>213</v>
+        <v>141</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>215</v>
+        <v>143</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>217</v>
+        <v>144</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>